--- a/school/Thesis Documentation/Digital/Numbers systems.xlsx
+++ b/school/Thesis Documentation/Digital/Numbers systems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\GitHub\Computer_HTL\school\Thesis Documentation\Digital\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\8Bit_Computer\school\Thesis Documentation\Digital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9761DE69-DF8D-48E8-801F-7E599E0BB527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEED6BC-AECA-4519-9824-4E45CE9BD22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40500" yWindow="-2340" windowWidth="11145" windowHeight="12555" xr2:uid="{A52A3322-E387-42A4-935B-5EB027D05D68}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A52A3322-E387-42A4-935B-5EB027D05D68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
   <si>
     <t>Decimal</t>
   </si>
@@ -74,16 +77,47 @@
     <t xml:space="preserve"> = 8</t>
   </si>
   <si>
-    <t xml:space="preserve"> = 128</t>
+    <t xml:space="preserve"> = -128</t>
+  </si>
+  <si>
+    <t>Places</t>
+  </si>
+  <si>
+    <t>Digits</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>inverted</t>
+  </si>
+  <si>
+    <t>binary value</t>
+  </si>
+  <si>
+    <t>value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -98,7 +132,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -349,13 +383,250 @@
       <bottom style="thick">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -393,57 +664,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -459,7 +826,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -775,20 +1142,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5FEAF3-73B7-4051-87AA-C3AF4D6635B8}">
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
     <col min="2" max="2" width="2.140625" customWidth="1"/>
     <col min="3" max="3" width="2.85546875" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
-    <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" customWidth="1"/>
-    <col min="8" max="8" width="2.28515625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="9" width="8.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="2.85546875" customWidth="1"/>
+    <col min="12" max="12" width="3.28515625" customWidth="1"/>
+    <col min="13" max="13" width="3.140625" customWidth="1"/>
+    <col min="14" max="15" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -796,7 +1168,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -809,20 +1181,34 @@
       <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="17">
-        <v>1</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="25">
-        <v>0</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>9</v>
+      <c r="F2" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="32"/>
+      <c r="H2" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="35"/>
+      <c r="K2" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="46">
+        <v>1</v>
+      </c>
+      <c r="M2" s="47">
+        <v>0</v>
+      </c>
+      <c r="N2" s="47">
+        <v>0</v>
+      </c>
+      <c r="O2" s="48">
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -835,20 +1221,34 @@
       <c r="D3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="19">
-        <v>2</v>
-      </c>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="14">
+        <v>1</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="26">
-        <v>1</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>4</v>
+      <c r="H3" s="21">
+        <v>0</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="36"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="46">
+        <v>0</v>
+      </c>
+      <c r="M3" s="47">
+        <v>0</v>
+      </c>
+      <c r="N3" s="47">
+        <v>1</v>
+      </c>
+      <c r="O3" s="48">
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,108 +1261,205 @@
       <c r="D4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="16">
+        <v>2</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="22">
+        <v>1</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="J4" s="36"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="39">
+        <v>0</v>
+      </c>
+      <c r="M4" s="40">
+        <v>0</v>
+      </c>
+      <c r="N4" s="40">
+        <v>1</v>
+      </c>
+      <c r="O4" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="13">
+        <v>142</v>
+      </c>
+      <c r="F5" s="16">
+        <v>4</v>
+      </c>
+      <c r="G5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="26">
-        <v>1</v>
-      </c>
-      <c r="I4" s="29" t="s">
+      <c r="H5" s="22">
+        <v>1</v>
+      </c>
+      <c r="I5" s="25" t="s">
         <v>10</v>
       </c>
+      <c r="J5" s="36"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="43">
+        <v>1</v>
+      </c>
+      <c r="M5" s="44">
+        <v>1</v>
+      </c>
+      <c r="N5" s="44">
+        <v>0</v>
+      </c>
+      <c r="O5" s="45">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="S5" s="54"/>
+      <c r="T5" s="54"/>
+      <c r="U5" s="58"/>
+      <c r="V5" s="38" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="15">
-        <v>142</v>
-      </c>
-      <c r="F5" s="19">
+    <row r="6" spans="1:22" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F6" s="16">
         <v>8</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="26">
-        <v>1</v>
-      </c>
-      <c r="I5" s="29" t="s">
+      <c r="H6" s="22">
+        <v>1</v>
+      </c>
+      <c r="I6" s="25" t="s">
         <v>11</v>
       </c>
+      <c r="J6" s="36"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="59">
+        <v>0</v>
+      </c>
+      <c r="S6" s="52">
+        <v>1</v>
+      </c>
+      <c r="T6" s="52">
+        <v>1</v>
+      </c>
+      <c r="U6" s="60">
+        <v>1</v>
+      </c>
+      <c r="V6" s="63">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F6" s="19">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F7" s="16">
         <v>16</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="26">
-        <v>0</v>
-      </c>
-      <c r="I6" s="29" t="s">
+      <c r="H7" s="22">
+        <v>0</v>
+      </c>
+      <c r="I7" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="J7" s="36"/>
+      <c r="Q7" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="R7" s="61">
+        <v>1</v>
+      </c>
+      <c r="S7" s="53">
+        <v>0</v>
+      </c>
+      <c r="T7" s="53">
+        <v>0</v>
+      </c>
+      <c r="U7" s="62">
+        <v>0</v>
+      </c>
+      <c r="V7" s="64">
+        <v>-8</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F7" s="19">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F8" s="16">
         <v>32</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G8" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="26">
-        <v>0</v>
-      </c>
-      <c r="I7" s="29" t="s">
+      <c r="H8" s="22">
+        <v>0</v>
+      </c>
+      <c r="I8" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="J8" s="36"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F8" s="19">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F9" s="16">
         <v>64</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G9" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="26">
-        <v>0</v>
-      </c>
-      <c r="I8" s="29" t="s">
+      <c r="H9" s="22">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25" t="s">
         <v>9</v>
       </c>
+      <c r="J9" s="36"/>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F9" s="21">
-        <v>128</v>
-      </c>
-      <c r="G9" s="22" t="s">
+    <row r="10" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="18">
+        <v>-128</v>
+      </c>
+      <c r="G10" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="27">
-        <v>1</v>
-      </c>
-      <c r="I9" s="30" t="s">
+      <c r="H10" s="23">
+        <v>1</v>
+      </c>
+      <c r="I10" s="26" t="s">
         <v>12</v>
       </c>
+      <c r="J10" s="36"/>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="23">
-        <v>142</v>
-      </c>
+    <row r="11" spans="1:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="F11" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="29"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="20">
+        <v>-110</v>
+      </c>
+      <c r="J11" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="R5:U5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/school/Thesis Documentation/Digital/Numbers systems.xlsx
+++ b/school/Thesis Documentation/Digital/Numbers systems.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\8Bit_Computer\school\Thesis Documentation\Digital\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\GitHub\Computer_HTL\school\Thesis Documentation\Digital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DEED6BC-AECA-4519-9824-4E45CE9BD22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7049299-F865-48F6-9480-F0E95D9411ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{A52A3322-E387-42A4-935B-5EB027D05D68}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A52A3322-E387-42A4-935B-5EB027D05D68}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>Decimal</t>
   </si>
@@ -95,20 +92,17 @@
     <t>+</t>
   </si>
   <si>
-    <t>inverted</t>
-  </si>
-  <si>
     <t>binary value</t>
   </si>
   <si>
-    <t>value</t>
+    <t>decimal value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,6 +112,14 @@
     </font>
     <font>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -550,9 +552,35 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
@@ -561,62 +589,32 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
         <color auto="1"/>
       </top>
       <bottom/>
@@ -626,117 +624,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -766,51 +660,173 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -826,7 +842,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1142,322 +1158,512 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5FEAF3-73B7-4051-87AA-C3AF4D6635B8}">
-  <dimension ref="A1:V11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="2.140625" customWidth="1"/>
-    <col min="3" max="3" width="2.85546875" customWidth="1"/>
-    <col min="4" max="4" width="6" customWidth="1"/>
+    <col min="1" max="4" width="9.140625" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="7.5703125" customWidth="1"/>
     <col min="7" max="7" width="7.140625" customWidth="1"/>
     <col min="8" max="9" width="8.140625" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="2.85546875" customWidth="1"/>
-    <col min="12" max="12" width="3.28515625" customWidth="1"/>
-    <col min="13" max="13" width="3.140625" customWidth="1"/>
-    <col min="14" max="15" width="3.28515625" customWidth="1"/>
+    <col min="10" max="11" width="9.140625" customWidth="1"/>
+    <col min="12" max="12" width="9.28515625" customWidth="1"/>
+    <col min="13" max="15" width="9.140625" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" t="s">
+    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24" t="s">
         <v>8</v>
       </c>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
-    <row r="2" spans="1:22" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+    <row r="2" spans="1:23" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="33" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="35">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="E2" s="24"/>
+      <c r="F2" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="38"/>
+      <c r="H2" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="35"/>
-      <c r="K2" s="49" t="s">
+      <c r="J2" s="1"/>
+      <c r="K2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="46">
-        <v>1</v>
-      </c>
-      <c r="M2" s="47">
-        <v>0</v>
-      </c>
-      <c r="N2" s="47">
-        <v>0</v>
-      </c>
-      <c r="O2" s="48">
+      <c r="L2" s="10">
+        <v>1</v>
+      </c>
+      <c r="M2" s="11">
+        <v>0</v>
+      </c>
+      <c r="N2" s="11">
+        <v>0</v>
+      </c>
+      <c r="O2" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:23" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="43">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="14">
-        <v>1</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="E3" s="24"/>
+      <c r="F3" s="45">
+        <v>1</v>
+      </c>
+      <c r="G3" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="21">
-        <v>0</v>
-      </c>
-      <c r="I3" s="24" t="s">
+      <c r="H3" s="47">
+        <v>0</v>
+      </c>
+      <c r="I3" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="36"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="46">
-        <v>0</v>
-      </c>
-      <c r="M3" s="47">
-        <v>0</v>
-      </c>
-      <c r="N3" s="47">
-        <v>1</v>
-      </c>
-      <c r="O3" s="48">
+      <c r="J3" s="2"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="11">
+        <v>0</v>
+      </c>
+      <c r="N3" s="11">
+        <v>1</v>
+      </c>
+      <c r="O3" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:23" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="51">
+        <v>1</v>
+      </c>
+      <c r="D4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="16">
+      <c r="E4" s="24"/>
+      <c r="F4" s="53">
         <v>2</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="22">
-        <v>1</v>
-      </c>
-      <c r="I4" s="25" t="s">
+      <c r="H4" s="55">
+        <v>1</v>
+      </c>
+      <c r="I4" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="36"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="39">
-        <v>0</v>
-      </c>
-      <c r="M4" s="40">
-        <v>0</v>
-      </c>
-      <c r="N4" s="40">
-        <v>1</v>
-      </c>
-      <c r="O4" s="41">
+      <c r="J4" s="2"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>1</v>
+      </c>
+      <c r="O4" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="13">
+    <row r="5" spans="1:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="59">
         <v>142</v>
       </c>
-      <c r="F5" s="16">
+      <c r="E5" s="24"/>
+      <c r="F5" s="53">
         <v>4</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="22">
-        <v>1</v>
-      </c>
-      <c r="I5" s="25" t="s">
+      <c r="H5" s="55">
+        <v>1</v>
+      </c>
+      <c r="I5" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="43">
-        <v>1</v>
-      </c>
-      <c r="M5" s="44">
-        <v>1</v>
-      </c>
-      <c r="N5" s="44">
-        <v>0</v>
-      </c>
-      <c r="O5" s="45">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="57" t="s">
+      <c r="J5" s="2"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="7">
+        <v>1</v>
+      </c>
+      <c r="M5" s="8">
+        <v>1</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" s="21"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="S5" s="54"/>
-      <c r="T5" s="54"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="38" t="s">
-        <v>20</v>
-      </c>
+      <c r="W5" s="24"/>
     </row>
-    <row r="6" spans="1:22" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F6" s="16">
+    <row r="6" spans="1:23" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="53">
         <v>8</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="22">
-        <v>1</v>
-      </c>
-      <c r="I6" s="25" t="s">
+      <c r="H6" s="55">
+        <v>1</v>
+      </c>
+      <c r="I6" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="59">
-        <v>0</v>
-      </c>
-      <c r="S6" s="52">
-        <v>1</v>
-      </c>
-      <c r="T6" s="52">
-        <v>1</v>
-      </c>
-      <c r="U6" s="60">
-        <v>1</v>
-      </c>
-      <c r="V6" s="63">
+      <c r="J6" s="2"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="18">
+        <v>0</v>
+      </c>
+      <c r="S6" s="13">
+        <v>1</v>
+      </c>
+      <c r="T6" s="13">
+        <v>1</v>
+      </c>
+      <c r="U6" s="14">
+        <v>1</v>
+      </c>
+      <c r="V6" s="25">
         <v>7</v>
       </c>
+      <c r="W6" s="24"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F7" s="16">
+    <row r="7" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="53">
         <v>16</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="22">
-        <v>0</v>
-      </c>
-      <c r="I7" s="25" t="s">
+      <c r="H7" s="55">
+        <v>0</v>
+      </c>
+      <c r="I7" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="Q7" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="R7" s="61">
-        <v>1</v>
-      </c>
-      <c r="S7" s="53">
-        <v>0</v>
-      </c>
-      <c r="T7" s="53">
-        <v>0</v>
-      </c>
-      <c r="U7" s="62">
-        <v>0</v>
-      </c>
-      <c r="V7" s="64">
+      <c r="J7" s="2"/>
+      <c r="Q7" s="17"/>
+      <c r="R7" s="26">
+        <v>1</v>
+      </c>
+      <c r="S7" s="27">
+        <v>0</v>
+      </c>
+      <c r="T7" s="27">
+        <v>0</v>
+      </c>
+      <c r="U7" s="28">
+        <v>0</v>
+      </c>
+      <c r="V7" s="29">
         <v>-8</v>
       </c>
+      <c r="W7" s="24"/>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F8" s="16">
+    <row r="8" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="53">
         <v>32</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="G8" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="22">
-        <v>0</v>
-      </c>
-      <c r="I8" s="25" t="s">
+      <c r="H8" s="55">
+        <v>0</v>
+      </c>
+      <c r="I8" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="J8" s="36"/>
+      <c r="J8" s="2"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F9" s="16">
+    <row r="9" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+      <c r="A9" s="24"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="53">
         <v>64</v>
       </c>
-      <c r="G9" s="17" t="s">
+      <c r="G9" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H9" s="22">
-        <v>0</v>
-      </c>
-      <c r="I9" s="25" t="s">
+      <c r="H9" s="55">
+        <v>0</v>
+      </c>
+      <c r="I9" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="J9" s="36"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="10">
+        <v>1</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+      <c r="N9" s="11">
+        <v>0</v>
+      </c>
+      <c r="O9" s="12">
+        <v>1</v>
+      </c>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
     </row>
-    <row r="10" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F10" s="18">
+    <row r="10" spans="1:23" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="60">
         <v>-128</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="23">
-        <v>1</v>
-      </c>
-      <c r="I10" s="26" t="s">
+      <c r="H10" s="62">
+        <v>1</v>
+      </c>
+      <c r="I10" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="36"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="10">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
+      <c r="N10" s="11">
+        <v>1</v>
+      </c>
+      <c r="O10" s="12">
+        <v>1</v>
+      </c>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
     </row>
-    <row r="11" spans="1:22" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="F11" s="29" t="s">
+    <row r="11" spans="1:23" ht="22.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="29"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="20">
+      <c r="G11" s="64"/>
+      <c r="H11" s="65"/>
+      <c r="I11" s="31">
         <v>-110</v>
       </c>
-      <c r="J11" s="37"/>
+      <c r="K11" s="70">
+        <v>1</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1</v>
+      </c>
+      <c r="O11" s="5">
+        <v>0</v>
+      </c>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="24"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+    </row>
+    <row r="12" spans="1:23" ht="21.75" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="K12" s="6"/>
+      <c r="L12" s="7">
+        <v>1</v>
+      </c>
+      <c r="M12" s="8">
+        <v>1</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9">
+        <v>0</v>
+      </c>
+      <c r="R12" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="S12" s="10">
+        <v>1</v>
+      </c>
+      <c r="T12" s="11">
+        <v>0</v>
+      </c>
+      <c r="U12" s="11">
+        <v>0</v>
+      </c>
+      <c r="V12" s="12">
+        <v>0</v>
+      </c>
+      <c r="W12" s="19">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="21" x14ac:dyDescent="0.25">
+      <c r="R13" s="15"/>
+      <c r="S13" s="10">
+        <v>0</v>
+      </c>
+      <c r="T13" s="11">
+        <v>0</v>
+      </c>
+      <c r="U13" s="11">
+        <v>0</v>
+      </c>
+      <c r="V13" s="12">
+        <v>1</v>
+      </c>
+      <c r="W13" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="K14" s="68"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="66">
+        <v>0</v>
+      </c>
+      <c r="T14" s="67">
+        <v>0</v>
+      </c>
+      <c r="U14" s="67">
+        <v>0</v>
+      </c>
+      <c r="V14" s="30"/>
+      <c r="W14" s="31"/>
+    </row>
+    <row r="15" spans="1:23" ht="21.75" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="R15" s="32"/>
+      <c r="S15" s="7">
+        <v>1</v>
+      </c>
+      <c r="T15" s="8">
+        <v>0</v>
+      </c>
+      <c r="U15" s="8">
+        <v>0</v>
+      </c>
+      <c r="V15" s="9">
+        <v>1</v>
+      </c>
+      <c r="W15" s="20">
+        <v>-7</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="F11:H11"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="R5:U5"/>
+    <mergeCell ref="R12:R14"/>
+    <mergeCell ref="K9:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/school/Thesis Documentation/Digital/Numbers systems.xlsx
+++ b/school/Thesis Documentation/Digital/Numbers systems.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\GitHub\Computer_HTL\school\Thesis Documentation\Digital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7049299-F865-48F6-9480-F0E95D9411ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A964F9C0-73F8-47B5-9AC7-8F1CBF96D5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{A52A3322-E387-42A4-935B-5EB027D05D68}"/>
   </bookViews>
@@ -102,7 +102,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +125,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -624,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -824,6 +831,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1573,7 +1581,9 @@
       <c r="W11" s="24"/>
     </row>
     <row r="12" spans="1:23" ht="21.75" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="K12" s="6"/>
+      <c r="K12" s="71">
+        <v>1</v>
+      </c>
       <c r="L12" s="7">
         <v>1</v>
       </c>
